--- a/test-env/testbooks/test-cases.xlsx
+++ b/test-env/testbooks/test-cases.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariano/Documents/projects/k8s-rightsizer/test-env/testbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785AFA6A-A6B4-D84B-960D-D968C16C8465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7CB112-3731-674F-A525-5096AF40860E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Base" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Recreate Params" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="57">
   <si>
     <t>Namespace</t>
   </si>
@@ -230,12 +231,123 @@
       <t>: Workload is paused.</t>
     </r>
   </si>
+  <si>
+    <t>test-sts-standard</t>
+  </si>
+  <si>
+    <t>redis</t>
+  </si>
+  <si>
+    <t>test-multi-container-sharding</t>
+  </si>
+  <si>
+    <t>100m
+10m
+10m</t>
+  </si>
+  <si>
+    <t>64Mi
+28Mi
+28Mi</t>
+  </si>
+  <si>
+    <t>test-recreate-strategy</t>
+  </si>
+  <si>
+    <r>
+      <t>Skip</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: UpdateStrategy Recreate</t>
+    </r>
+  </si>
+  <si>
+    <t>busybox</t>
+  </si>
+  <si>
+    <t>32Mi</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Resize saltato perché </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>UpdateStrategy=Recreate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, possibile downtime</t>
+    </r>
+  </si>
+  <si>
+    <t>Resize completato con successo, rollout completato e workload stabile</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Resize saltato perché </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>UpdateStrategy=OnDelete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, modifica senza effetto</t>
+    </r>
+  </si>
+  <si>
+    <t>Skipping resize due to pbd restrictions</t>
+  </si>
+  <si>
+    <t>Resized correctly</t>
+  </si>
+  <si>
+    <t>Tested on Remote env</t>
+  </si>
+  <si>
+    <t>main-app
+sidecar-1
+sidecar-2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,11 +363,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -286,6 +398,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -307,32 +431,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -614,240 +752,335 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="100" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="2" max="2" width="20.5" style="9" customWidth="1"/>
     <col min="3" max="4" width="17.33203125" customWidth="1"/>
     <col min="5" max="5" width="16.33203125" customWidth="1"/>
     <col min="6" max="6" width="18.1640625" customWidth="1"/>
     <col min="7" max="7" width="34.5" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" style="10" customWidth="1"/>
-    <col min="9" max="9" width="42.1640625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="42.1640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="12" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="8"/>
-    </row>
-    <row r="3" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="H10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="14"/>
+    </row>
+    <row r="11" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B11" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="8"/>
-    </row>
-    <row r="4" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="8"/>
-    </row>
-    <row r="5" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="D11" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="8"/>
-    </row>
-    <row r="6" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="7" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
-    </row>
-    <row r="9" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-    </row>
-    <row r="10" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="F11" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -860,4 +1093,90 @@
     <oddHeader>&amp;C&amp;"Arial"&amp;8&amp;K000000 INTERNAL&amp;1#_x000D_</oddHeader>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{036162D0-F9D6-254B-8FA3-05C8D06B66A6}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="100" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.5" style="9" customWidth="1"/>
+    <col min="3" max="4" width="17.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.1640625" customWidth="1"/>
+    <col min="7" max="7" width="34.5" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="42.1640625" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576" xr:uid="{D2B5B0FA-9700-454C-AAFF-B6879D81FD91}">
+      <formula1>"KO,OK"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Arial"&amp;8&amp;K000000 INTERNAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
+</worksheet>
 </file>
--- a/test-env/testbooks/test-cases.xlsx
+++ b/test-env/testbooks/test-cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariano/Documents/projects/k8s-rightsizer/test-env/testbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7CB112-3731-674F-A525-5096AF40860E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57275E98-050C-F548-AE69-134AFA545BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Base" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="58">
   <si>
     <t>Namespace</t>
   </si>
@@ -341,6 +341,9 @@
     <t>main-app
 sidecar-1
 sidecar-2</t>
+  </si>
+  <si>
+    <t>test-workload-strategy</t>
   </si>
 </sst>
 </file>
@@ -752,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="100" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.83203125" customWidth="1"/>
@@ -1081,6 +1084,33 @@
       <c r="I11" s="9" t="s">
         <v>50</v>
       </c>
+    </row>
+    <row r="12" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/test-env/testbooks/test-cases.xlsx
+++ b/test-env/testbooks/test-cases.xlsx
@@ -8,25 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariano/Documents/projects/k8s-rightsizer/test-env/testbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57275E98-050C-F548-AE69-134AFA545BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE879981-C8C6-2846-B027-1C2BA3BED49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Base" sheetId="1" r:id="rId1"/>
     <sheet name="Test Recreate Params" sheetId="3" r:id="rId2"/>
+    <sheet name="Test limits" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="70">
   <si>
     <t>Namespace</t>
   </si>
@@ -345,12 +357,120 @@
   <si>
     <t>test-workload-strategy</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Test Execution Params</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+RESIZE_ON_RECREATE=true
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Test Execution Params</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:
+WORKERS=3
+RESIZE_STRATEGY=container (or worklaod according the test)</t>
+    </r>
+  </si>
+  <si>
+    <t>48Mi</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Test Execution Params</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:
+WORKERS=3
+USE_LIMITS=true
+RESIZE_ON_RECREATE=true</t>
+    </r>
+  </si>
+  <si>
+    <t>TargetCPU Request</t>
+  </si>
+  <si>
+    <t>TargetMemory Request</t>
+  </si>
+  <si>
+    <t>TargetCPU Limit</t>
+  </si>
+  <si>
+    <t>TargetMemory Limit</t>
+  </si>
+  <si>
+    <t>150m
+20m
+10m</t>
+  </si>
+  <si>
+    <t>200m
+10m
+10m</t>
+  </si>
+  <si>
+    <t>95Mi
+32Mi
+28Mi</t>
+  </si>
+  <si>
+    <t>48Mi
+48Mi
+48Mi</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,6 +533,13 @@
       <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -434,7 +561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
@@ -474,6 +601,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -755,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="100" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.83203125" customWidth="1"/>
@@ -769,61 +902,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+    </row>
+    <row r="2" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I2" s="12" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
@@ -831,19 +948,19 @@
         <v>27</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>33</v>
@@ -860,28 +977,28 @@
         <v>27</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
@@ -889,28 +1006,28 @@
         <v>27</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
@@ -918,28 +1035,28 @@
         <v>27</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
@@ -947,24 +1064,24 @@
         <v>27</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="15" t="s">
         <v>49</v>
       </c>
       <c r="I7" s="9" t="s">
@@ -976,7 +1093,7 @@
         <v>27</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>7</v>
@@ -985,13 +1102,13 @@
         <v>32</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>49</v>
@@ -1005,22 +1122,22 @@
         <v>27</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>49</v>
@@ -1034,87 +1151,119 @@
         <v>27</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>44</v>
+      <c r="D10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I10" s="14"/>
+      <c r="I10" s="9" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>45</v>
+      <c r="B11" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>48</v>
+      <c r="D11" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>50</v>
-      </c>
+      <c r="I11" s="14"/>
     </row>
     <row r="12" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>57</v>
+      <c r="B12" s="13" t="s">
+        <v>45</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>44</v>
+      <c r="D12" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="I12" s="14"/>
+      <c r="I12" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="14"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576" xr:uid="{8A2AEFCE-2816-432B-ADDD-66CB218CB11D}">
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576" xr:uid="{8A2AEFCE-2816-432B-ADDD-66CB218CB11D}">
       <formula1>"KO,OK"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1127,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{036162D0-F9D6-254B-8FA3-05C8D06B66A6}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="100" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.83203125" customWidth="1"/>
@@ -1141,66 +1290,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+    </row>
+    <row r="2" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I2" s="12" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="3" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F3" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>54</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576" xr:uid="{D2B5B0FA-9700-454C-AAFF-B6879D81FD91}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576" xr:uid="{D2B5B0FA-9700-454C-AAFF-B6879D81FD91}">
       <formula1>"KO,OK"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1209,4 +1374,241 @@
     <oddHeader>&amp;C&amp;"Arial"&amp;8&amp;K000000 INTERNAL&amp;1#_x000D_</oddHeader>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2EB0D0-ED05-7344-9AEA-3345F5FD20F7}">
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="28.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+    </row>
+    <row r="2" spans="1:11" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="9"/>
+    </row>
+    <row r="4" spans="1:11" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="9"/>
+    </row>
+    <row r="5" spans="1:11" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="14"/>
+    </row>
+    <row r="6" spans="1:11" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="9"/>
+    </row>
+    <row r="7" spans="1:11" ht="100" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J7" xr:uid="{E1DA62D3-5E7A-8D49-A15E-52C661FE61FE}">
+      <formula1>"KO,OK"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>